--- a/outputs/daily/hr_rankings_2026-10-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-17.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1569,7 @@
         <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1583,39 +1583,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1760,7 +1756,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1832,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1856,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1870,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1883,7 @@
         <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1901,39 +1897,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2078,7 +2070,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,24 +2121,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2154,22 +2146,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2178,7 +2170,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,26 +2184,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2211,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,12 +2259,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2286,12 +2274,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2301,102 +2289,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,12 +2435,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2472,12 +2460,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2514,7 +2502,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>32</v>
@@ -2523,13 +2511,13 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2547,7 +2535,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2589,12 +2577,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,7 +2592,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2619,67 +2607,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2714,7 +2702,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,24 +2753,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2790,22 +2778,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2828,26 +2816,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2865,7 +2853,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2907,12 +2895,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2922,12 +2910,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2937,102 +2925,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3088,7 +3076,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,7 +3096,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3132,7 +3120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3134,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3147,7 @@
         <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -3173,39 +3161,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3334,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3426,7 +3410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3450,7 +3434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3448,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3461,7 @@
         <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3491,39 +3475,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3668,7 +3648,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3744,7 +3724,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3768,7 +3748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3762,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3775,7 @@
         <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3809,39 +3789,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3986,7 +3962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4062,7 +4038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4086,7 +4062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,7 +4076,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -4113,7 +4089,7 @@
         <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -4127,39 +4103,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4304,7 +4276,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,7 +4352,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4622,7 +4594,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4670,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4694,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4708,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4721,7 @@
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4763,39 +4735,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4940,7 +4908,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,24 +4959,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5016,7 +4984,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5026,12 +4994,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5040,7 +5008,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,26 +5022,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5049,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,12 +5097,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5112,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,102 +5127,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,24 +5273,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5334,7 +5298,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5344,12 +5308,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5358,7 +5322,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,14 +5336,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>43.6</v>
@@ -5388,10 +5352,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5451,12 +5415,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,12 +5430,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,102 +5445,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,7 +5616,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5894,7 +5858,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5970,7 +5934,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6212,7 +6176,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6252,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6530,7 +6494,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,7 +6976,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7254,7 +7218,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7330,7 +7294,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7574,7 +7538,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7654,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7678,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7692,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7705,7 @@
         <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7755,39 +7719,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7932,7 +7892,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7968,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7992,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +8006,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +8019,7 @@
         <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -8073,39 +8033,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8250,7 +8206,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,24 +8257,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8326,22 +8282,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8350,7 +8306,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,26 +8320,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8347,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,12 +8395,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8458,12 +8410,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8473,102 +8425,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,12 +8571,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8644,12 +8596,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8686,7 +8638,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>32</v>
@@ -8695,13 +8647,13 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8719,7 +8671,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8761,12 +8713,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,7 +8728,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8791,67 +8743,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8886,7 +8838,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,24 +8889,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8962,22 +8914,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9000,26 +8952,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9037,7 +8989,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -9079,12 +9031,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9094,12 +9046,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9109,102 +9061,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9260,7 +9212,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,7 +9232,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9304,7 +9256,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9270,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9283,7 @@
         <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -9345,39 +9297,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9470,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9598,7 +9546,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9622,7 +9570,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9584,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9597,7 @@
         <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -9663,39 +9611,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9840,7 +9784,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9916,7 +9860,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9940,7 +9884,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9898,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9911,7 @@
         <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -9981,39 +9925,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10158,7 +10098,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10234,7 +10174,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10258,7 +10198,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,7 +10212,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -10285,7 +10225,7 @@
         <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -10299,39 +10239,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10476,7 +10412,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10552,7 +10488,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10794,7 +10730,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10806,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10830,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10844,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10857,7 @@
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10935,39 +10871,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11112,7 +11044,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,24 +11095,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -11188,7 +11120,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11198,12 +11130,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11212,7 +11144,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,26 +11158,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11185,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,12 +11233,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11248,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,102 +11263,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,24 +11409,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -11506,7 +11434,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11516,12 +11444,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11530,7 +11458,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,14 +11472,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>43.6</v>
@@ -11560,10 +11488,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11623,12 +11551,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,12 +11566,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,102 +11581,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,7 +11752,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12066,7 +11994,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12142,7 +12070,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12384,7 +12312,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12388,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12702,7 +12630,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-17.xlsx
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.3</v>
+        <v>53</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1163,7 +1159,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.2</v>
+        <v>52.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1225,39 +1221,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2121,24 +2113,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2151,17 +2143,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2170,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2188,22 +2180,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2221,7 +2213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2259,27 +2251,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2289,97 +2281,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2440,7 +2432,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2484,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2498,7 +2490,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2511,7 +2503,7 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2525,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2753,24 +2741,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2783,17 +2771,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2802,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2816,26 +2804,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2843,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2895,12 +2879,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2910,12 +2894,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2925,97 +2909,97 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -4327,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4376,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38.2</v>
+        <v>37.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4390,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -4403,13 +4387,13 @@
         <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4417,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4469,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4499,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4645,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4675,17 +4655,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4694,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4708,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4745,7 +4725,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4783,27 +4763,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4813,97 +4793,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4959,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4989,7 +4969,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5008,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.4</v>
+        <v>36.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5022,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5059,7 +5039,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -5097,27 +5077,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5127,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5273,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5303,7 +5283,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5322,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.9</v>
+        <v>35.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5336,11 +5316,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -5349,13 +5329,13 @@
         <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5363,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5415,22 +5391,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -5445,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5591,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5621,7 +5597,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5640,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.2</v>
+        <v>35.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5654,11 +5630,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -5667,13 +5643,13 @@
         <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5681,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5733,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5748,7 +5720,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -5763,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5909,24 +5881,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5939,17 +5911,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5958,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.2</v>
+        <v>34.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5972,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5999,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6051,27 +6019,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6081,97 +6049,97 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -6276,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6290,7 +6258,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6303,7 +6271,7 @@
         <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6317,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7000,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.3</v>
+        <v>53</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7014,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7027,7 +6991,7 @@
         <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7041,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7299,7 +7259,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7318,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.2</v>
+        <v>52.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7332,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7345,7 +7305,7 @@
         <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7361,39 +7321,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8257,24 +8213,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8287,17 +8243,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8306,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8324,22 +8280,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8357,7 +8313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8395,27 +8351,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8425,97 +8381,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -8576,7 +8532,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8620,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8634,7 +8590,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8647,7 +8603,7 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -8661,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8889,24 +8841,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8919,17 +8871,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8938,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8952,26 +8904,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8979,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9031,12 +8979,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9046,12 +8994,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9061,97 +9009,97 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -10463,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10512,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38.2</v>
+        <v>37.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10526,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -10539,13 +10487,13 @@
         <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10553,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10605,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10635,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10781,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -10811,17 +10755,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10830,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10844,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10881,7 +10825,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10919,27 +10863,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10949,97 +10893,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -11095,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11125,7 +11069,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11144,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.4</v>
+        <v>36.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11158,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11195,7 +11139,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -11233,27 +11177,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11263,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11409,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11439,7 +11383,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11458,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.9</v>
+        <v>35.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11472,11 +11416,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -11485,13 +11429,13 @@
         <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11499,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11551,22 +11491,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -11581,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11727,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11757,7 +11697,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11776,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.2</v>
+        <v>35.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11790,11 +11730,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -11803,13 +11743,13 @@
         <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11817,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11869,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11884,7 +11820,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -11899,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12045,24 +11981,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -12075,17 +12011,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12094,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.2</v>
+        <v>34.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12108,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12135,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12187,27 +12119,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12217,97 +12149,97 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -12412,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12426,7 +12358,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -12439,7 +12371,7 @@
         <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -12453,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-10-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-17.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.6</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.3</v>
+        <v>47.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2705,17 +2705,17 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3333,17 +3333,17 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3961,17 +3961,17 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4589,17 +4589,17 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4903,17 +4903,17 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.8</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5531,17 +5531,17 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.4</v>
+        <v>32.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.2</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6473,17 +6473,17 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7193,17 +7193,17 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.6</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7863,17 +7863,17 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8177,17 +8177,17 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.3</v>
+        <v>47.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9747,17 +9747,17 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10061,17 +10061,17 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10375,17 +10375,17 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11003,17 +11003,17 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11088,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11317,17 +11317,17 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.8</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11631,17 +11631,17 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11945,17 +11945,17 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.4</v>
+        <v>32.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12259,17 +12259,17 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.2</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -12573,17 +12573,17 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
